--- a/연구코드/results/regression/sinchon/female/regression_results.xlsx
+++ b/연구코드/results/regression/sinchon/female/regression_results.xlsx
@@ -557,13 +557,13 @@
         <v>0.0327</v>
       </c>
       <c r="M2">
-        <v>0.748</v>
+        <v>0.6228</v>
       </c>
       <c r="N2">
-        <v>0.0781</v>
+        <v>0.8303</v>
       </c>
       <c r="O2">
-        <v>0.9643</v>
+        <v>0.5552</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -604,13 +604,13 @@
         <v>0.0376</v>
       </c>
       <c r="M3">
-        <v>0.7417</v>
+        <v>0.661</v>
       </c>
       <c r="N3">
-        <v>0.0716</v>
+        <v>0.734</v>
       </c>
       <c r="O3">
-        <v>0.958</v>
+        <v>0.6375</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -651,13 +651,13 @@
         <v>0.0256</v>
       </c>
       <c r="M4">
-        <v>0.7369</v>
+        <v>0.6481</v>
       </c>
       <c r="N4">
-        <v>0.1237</v>
+        <v>0.78</v>
       </c>
       <c r="O4">
-        <v>0.9349</v>
+        <v>0.6059</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -698,13 +698,13 @@
         <v>0.0351</v>
       </c>
       <c r="M5">
-        <v>0.7195</v>
+        <v>0.6118</v>
       </c>
       <c r="N5">
-        <v>0.1237</v>
+        <v>0.7654</v>
       </c>
       <c r="O5">
-        <v>0.912</v>
+        <v>0.5618</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -745,13 +745,13 @@
         <v>0.0213</v>
       </c>
       <c r="M6">
-        <v>0.7163</v>
+        <v>0.607</v>
       </c>
       <c r="N6">
-        <v>0.1428</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="O6">
-        <v>0.9015</v>
+        <v>0.5536</v>
       </c>
     </row>
   </sheetData>
